--- a/tame_output/ON/bt/strategyON_20231111.xlsx
+++ b/tame_output/ON/bt/strategyON_20231111.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>133.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1777"/>
+  <dimension ref="A1:G1778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.126357332773642</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42397,6 +42397,29 @@
       </c>
       <c r="G1777" t="n">
         <v>4.386785924927612</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="B1778" t="n">
+        <v>3.132430425955549</v>
+      </c>
+      <c r="C1778" t="n">
+        <v>3.081785372698861</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>1.544789511760652</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>3.699344753089375</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>2.177212046409986</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>4.388112600544854</v>
       </c>
     </row>
   </sheetData>
